--- a/AAAGameData/DataTables/ChessEXPRuleTable.xlsx
+++ b/AAAGameData/DataTables/ChessEXPRuleTable.xlsx
@@ -108,14 +108,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -571,164 +564,160 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1171,13 +1160,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
@@ -1190,13 +1179,13 @@
         <v>2</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>2</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="3">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -1209,13 +1198,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>2</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
@@ -1228,13 +1217,13 @@
         <v>4</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>3</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -1243,9 +1232,9 @@
     </row>
     <row r="9" spans="1:7">
       <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:7">
       <c r="C10" s="3"/>
